--- a/web/files/九龙-何文田-芳菲.xlsx
+++ b/web/files/九龙-何文田-芳菲.xlsx
@@ -3272,7 +3272,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -3458,34 +3458,34 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
-        <v>14404000</v>
+        <v>12964000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>29946</v>
+        <v>26952</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="5" t="n">
-        <v>11091080</v>
+        <v>12964000</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>23058</v>
+        <v>26952</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -5695,12 +5695,12 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>A | 481呎 (2房)
 $1455万
 $30,241/呎
-(暂停销售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -5726,12 +5726,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 481呎 (2房)
-$1440万
-$29,946/呎
-(已定价未售)</t>
+$1296万
+$26,952/呎
+(26年-09月-07日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">

--- a/web/files/九龙-何文田-芳菲.xlsx
+++ b/web/files/九龙-何文田-芳菲.xlsx
@@ -3272,34 +3272,34 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
-        <v>14546000</v>
+        <v>13091000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>30241</v>
+        <v>27216</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>11200420</v>
+        <v>13091000</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>23286</v>
+        <v>27216</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5695,12 +5695,12 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 481呎 (2房)
-$1455万
-$30,241/呎
-(已定价未售)</t>
+$1309万
+$27,216/呎
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">

--- a/web/files/九龙-何文田-芳菲.xlsx
+++ b/web/files/九龙-何文田-芳菲.xlsx
@@ -2714,7 +2714,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -5602,12 +5602,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>A | 465呎 (2房)
 $1462万
 $31,439/呎
-(暂停销售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">

--- a/web/files/九龙-何文田-芳菲.xlsx
+++ b/web/files/九龙-何文田-芳菲.xlsx
@@ -3277,7 +3277,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -5700,7 +5700,7 @@
           <t>A | 481呎 (2房)
 $1309万
 $27,216/呎
-(26年-09月-10日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -5731,7 +5731,7 @@
           <t>A | 481呎 (2房)
 $1296万
 $26,952/呎
-(26年-09月-07日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">

--- a/web/files/九龙-何文田-芳菲.xlsx
+++ b/web/files/九龙-何文田-芳菲.xlsx
@@ -2714,7 +2714,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -5602,12 +5602,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 465呎 (2房)
 $1462万
 $31,439/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">

--- a/web/files/九龙-何文田-芳菲.xlsx
+++ b/web/files/九龙-何文田-芳菲.xlsx
@@ -994,14 +994,14 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>8103480</v>
+        <v>8682300</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>28334</v>
+        <v>30358</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -1056,14 +1056,14 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>12614140</v>
+        <v>13515150</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>27127</v>
+        <v>29065</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1118,14 +1118,14 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>10699150</v>
+        <v>11463375</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>25843</v>
+        <v>27689</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -1180,14 +1180,14 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>7954100</v>
+        <v>8522250</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>27812</v>
+        <v>29798</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -1242,14 +1242,14 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>12375440</v>
+        <v>13259400</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>26614</v>
+        <v>28515</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1304,14 +1304,14 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>10595200</v>
+        <v>11352000</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>25592</v>
+        <v>27420</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1366,14 +1366,14 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>7631470</v>
+        <v>8176575</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>26683</v>
+        <v>28589</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1428,14 +1428,14 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>12677280</v>
+        <v>13582800</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>26356</v>
+        <v>28239</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
@@ -1490,14 +1490,14 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>10492790</v>
+        <v>11242275</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>25345</v>
+        <v>27155</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1552,14 +1552,14 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>7558320</v>
+        <v>8098200</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>26428</v>
+        <v>28315</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1614,14 +1614,14 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>12556390</v>
+        <v>13453275</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>26105</v>
+        <v>27969</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -1676,14 +1676,14 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>10390380</v>
+        <v>11132550</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>25098</v>
+        <v>26890</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -1738,14 +1738,14 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>7485940</v>
+        <v>8020650</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>26175</v>
+        <v>28044</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -1800,14 +1800,14 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>11820270</v>
+        <v>12664575</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>25420</v>
+        <v>27236</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -1924,14 +1924,14 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>7414330</v>
+        <v>7943925</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>25924</v>
+        <v>27776</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
@@ -1986,14 +1986,14 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>11705540</v>
+        <v>12541650</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>25173</v>
+        <v>26971</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -2048,14 +2048,14 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>10189410</v>
+        <v>10917225</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>24612</v>
+        <v>26370</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
@@ -2110,14 +2110,14 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>7344260</v>
+        <v>7868850</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>25679</v>
+        <v>27513</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2172,14 +2172,14 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>11592350</v>
+        <v>12420375</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>24930</v>
+        <v>26710</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>10089310</v>
+        <v>10809975</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>24370</v>
+        <v>26111</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
@@ -2296,14 +2296,14 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>7274190</v>
+        <v>7793775</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>25434</v>
+        <v>27251</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
@@ -2358,14 +2358,14 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>11873400</v>
+        <v>12721500</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>24685</v>
+        <v>26448</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
@@ -2668,14 +2668,14 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>7010850</v>
+        <v>7511625</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>24513</v>
+        <v>26264</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -2714,34 +2714,34 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
-        <v>14619000</v>
+        <v>13157000</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>31439</v>
+        <v>28295</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>11256630</v>
+        <v>13157000</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>24208</v>
+        <v>28295</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -2792,14 +2792,14 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>9705080</v>
+        <v>10398300</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>23442</v>
+        <v>25117</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
@@ -3350,14 +3350,14 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K44" s="5" t="n">
-        <v>9426340</v>
+        <v>10099650</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>22769</v>
+        <v>24395</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
@@ -3722,14 +3722,14 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K50" s="5" t="n">
-        <v>9243850</v>
+        <v>9904125</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>22328</v>
+        <v>23923</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
@@ -4590,14 +4590,14 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="K64" s="5" t="n">
-        <v>10016930</v>
+        <v>10732425</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>21542</v>
+        <v>23080</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5602,12 +5602,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 465呎 (2房)
-$1462万
-$31,439/呎
-(在售)</t>
+$1316万
+$28,295/呎
+(26年-10月-19日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
